--- a/dist/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월)_대시보드포함.xlsx
+++ b/dist/(aT&KPC) 실적취합양식_2026 aT농산물온라인마케터_분석(8월)_대시보드포함.xlsx
@@ -36,7 +36,7 @@
     <numFmt numFmtId="166" formatCode="###\-##\-#####"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -306,6 +306,12 @@
       <color rgb="001E293B"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="25">
     <fill>
@@ -449,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -698,6 +704,20 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -733,7 +753,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1299,6 +1319,22 @@
     </xf>
     <xf numFmtId="167" fontId="27" fillId="21" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="39" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="12" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3040,52 +3076,95 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="211" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="C8" s="212">
+        <f>SUM(D8,K8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="213">
+        <f>SUM(E8:J8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="214" t="n">
+        <v>93</v>
+      </c>
+      <c r="F8" s="214" t="n">
+        <v>41</v>
+      </c>
+      <c r="G8" s="214" t="n">
+        <v>34</v>
+      </c>
+      <c r="H8" s="214" t="n">
+        <v>19</v>
+      </c>
+      <c r="I8" s="214" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="214" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" s="215">
+        <f>SUM(L8:M8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="214" t="n">
+        <v>18</v>
+      </c>
+      <c r="M8" s="214" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>상품수</t>
         </is>
       </c>
-      <c r="C8" s="41">
-        <f>D8+K8</f>
-        <v/>
-      </c>
-      <c r="D8" s="42">
-        <f>SUM(E8:J8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="43">
+      <c r="C9" s="41">
+        <f>D9+K9</f>
+        <v/>
+      </c>
+      <c r="D9" s="42">
+        <f>SUM(E9:J9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,E$5)</f>
         <v/>
       </c>
-      <c r="F8" s="43">
+      <c r="F9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,F$5)</f>
         <v/>
       </c>
-      <c r="G8" s="43">
+      <c r="G9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,G$5)</f>
         <v/>
       </c>
-      <c r="H8" s="43">
+      <c r="H9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,H$5)</f>
         <v/>
       </c>
-      <c r="I8" s="43">
+      <c r="I9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,I$5)</f>
         <v/>
       </c>
-      <c r="J8" s="43">
+      <c r="J9" s="216">
         <f>COUNTIF(①농산물raw!$A$6:$A$1454,J$5)</f>
         <v/>
       </c>
-      <c r="K8" s="44">
-        <f>SUM(L8:M8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="43">
+      <c r="K9" s="44">
+        <f>SUM(L9:M9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="216">
         <f>COUNTIF(②유기농raw!$A$6:$A$207,L$5)</f>
         <v/>
       </c>
-      <c r="M8" s="43">
+      <c r="M9" s="216">
         <f>COUNTIF(②유기농raw!$A$6:$A$207,M$5)</f>
         <v/>
       </c>
